--- a/Project_3_PD Day_Dashboard/3_PD Day_Dashboard.xlsx
+++ b/Project_3_PD Day_Dashboard/3_PD Day_Dashboard.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Professional Development Day\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Excel_Data Anaylst_Course\Excel_Project_Data_Analyst\Excel_Project_Data_Analystics\Project_3_PD Day_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A159DF-E4C9-4CFA-B24D-08065AE450CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68F84B6-5033-4573-AE49-E814DA328015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10200" yWindow="0" windowWidth="10200" windowHeight="10920" xr2:uid="{4EA5E3DA-7CC3-49AA-9AB1-72874511159F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{4EA5E3DA-7CC3-49AA-9AB1-72874511159F}"/>
   </bookViews>
   <sheets>
-    <sheet name="data_school_date" sheetId="2" r:id="rId1"/>
+    <sheet name="data_school_date" sheetId="2" state="hidden" r:id="rId1"/>
     <sheet name="Calculator" sheetId="1" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" r:id="rId3"/>
-    <sheet name="Pivot Table" sheetId="4" r:id="rId4"/>
+    <sheet name="Validation" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Pivot Table" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Date">Calculator!$B$8</definedName>
@@ -1282,9 +1282,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1310,6 +1307,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -76251,21 +76252,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="11" t="str">
+      <c r="B3" s="10" t="str">
         <f>Validation!G2</f>
         <v>16 Apr 2027 - 54 Schools Can Attend</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <f>Validation!C2</f>
         <v>54</v>
       </c>
@@ -76273,55 +76274,56 @@
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
-      <c r="B8" s="4">
+      <c r="B8" s="14">
         <v>46493</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>347</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="12" spans="1:10" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <f>Validation!F2</f>
         <v>0.17704918032786884</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <f>Validation!$E$2</f>
         <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="2">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B16:J17"/>
@@ -76405,11 +76407,11 @@
         <f>COUNTA(_xlfn.UNIQUE(data_school_date[Schools]))</f>
         <v>305</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <f>(C2/E2)</f>
         <v>0.17704918032786884</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <f>TEXT(Date,"DD MMM YYY") &amp; " - " &amp; C2 &amp; " Schools Can Attend"</f>
         <v>16 Apr 2027 - 54 Schools Can Attend</v>
       </c>
@@ -76432,8 +76434,8 @@
         <f>COUNTIFS(data_school_date[Province],$A3,data_school_date[Date],Date)</f>
         <v>8</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
       <c r="I3" s="1">
         <v>46416</v>
       </c>
@@ -76452,9 +76454,9 @@
         <f>COUNTIFS(data_school_date[Province],$A4,data_school_date[Date],Date)</f>
         <v>10</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
       <c r="I4" s="1">
         <v>46528</v>
       </c>
@@ -76705,7 +76707,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B3">
@@ -76713,7 +76715,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>153</v>
       </c>
       <c r="B4">
@@ -76721,7 +76723,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B5">
@@ -76729,7 +76731,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B6">
@@ -76737,7 +76739,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B7">
@@ -76745,7 +76747,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B8">
@@ -76761,7 +76763,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B10">
@@ -76769,7 +76771,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B11">
@@ -76777,7 +76779,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B12">
@@ -76785,7 +76787,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B13">
@@ -76793,7 +76795,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B14">
@@ -76801,7 +76803,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B15">
@@ -76817,7 +76819,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B17">
@@ -76825,7 +76827,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B18">
@@ -76833,7 +76835,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>226</v>
       </c>
       <c r="B19">
@@ -76841,7 +76843,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B20">
@@ -76849,7 +76851,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B21">
@@ -76865,7 +76867,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B23">
@@ -76873,7 +76875,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B24">
@@ -76881,7 +76883,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="11" t="s">
         <v>226</v>
       </c>
       <c r="B25">
@@ -76889,7 +76891,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B26">
@@ -76897,7 +76899,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B27">
@@ -76913,7 +76915,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B29">
@@ -76921,7 +76923,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B30">
@@ -76929,7 +76931,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B31">
@@ -76937,7 +76939,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B32">
@@ -76945,7 +76947,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B33">
@@ -76953,7 +76955,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B34">
@@ -76961,7 +76963,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B35">
@@ -76977,7 +76979,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B37">
@@ -76985,7 +76987,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B38">
@@ -76993,7 +76995,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B39">
@@ -77001,7 +77003,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B40">
@@ -77009,7 +77011,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="11" t="s">
         <v>149</v>
       </c>
       <c r="B41">
@@ -77017,7 +77019,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B42">
@@ -77025,7 +77027,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B43">
@@ -77033,7 +77035,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B44">
@@ -77049,7 +77051,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B46">
@@ -77057,7 +77059,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B47">
@@ -77065,7 +77067,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B48">
@@ -77073,7 +77075,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B49">
@@ -77081,7 +77083,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B50">
@@ -77089,7 +77091,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B51">
@@ -77105,7 +77107,7 @@
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B53">
@@ -77113,7 +77115,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B54">
@@ -77121,7 +77123,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B55">
@@ -77129,7 +77131,7 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B56">
@@ -77145,7 +77147,7 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B58">
@@ -77153,7 +77155,7 @@
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B59">
@@ -77161,7 +77163,7 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="11" t="s">
         <v>226</v>
       </c>
       <c r="B60">
@@ -77169,7 +77171,7 @@
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B61">
@@ -77177,7 +77179,7 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B62">
@@ -77193,7 +77195,7 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B64">
@@ -77201,7 +77203,7 @@
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
+      <c r="A65" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B65">
@@ -77209,7 +77211,7 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B66">
@@ -77217,7 +77219,7 @@
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B67">
@@ -77225,7 +77227,7 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B68">
@@ -77233,7 +77235,7 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B69">
@@ -77249,7 +77251,7 @@
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B71">
@@ -77257,7 +77259,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
+      <c r="A72" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B72">
@@ -77265,7 +77267,7 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
+      <c r="A73" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B73">
@@ -77273,7 +77275,7 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
+      <c r="A74" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B74">
@@ -77281,7 +77283,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
+      <c r="A75" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B75">
@@ -77289,7 +77291,7 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
+      <c r="A76" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B76">
@@ -77305,7 +77307,7 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
+      <c r="A78" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B78">
@@ -77313,7 +77315,7 @@
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
+      <c r="A79" s="11" t="s">
         <v>153</v>
       </c>
       <c r="B79">
@@ -77321,7 +77323,7 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="12" t="s">
+      <c r="A80" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B80">
@@ -77329,7 +77331,7 @@
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B81">
@@ -77345,7 +77347,7 @@
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B83">
@@ -77353,7 +77355,7 @@
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
+      <c r="A84" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B84">
@@ -77361,7 +77363,7 @@
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="11" t="s">
         <v>226</v>
       </c>
       <c r="B85">
@@ -77369,7 +77371,7 @@
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
+      <c r="A86" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B86">
@@ -77377,7 +77379,7 @@
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B87">
@@ -77385,7 +77387,7 @@
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="12" t="s">
+      <c r="A88" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B88">
@@ -77393,7 +77395,7 @@
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="12" t="s">
+      <c r="A89" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B89">
@@ -77401,7 +77403,7 @@
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="12" t="s">
+      <c r="A90" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B90">
@@ -77417,7 +77419,7 @@
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="12" t="s">
+      <c r="A92" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B92">
@@ -77425,7 +77427,7 @@
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="12" t="s">
+      <c r="A93" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B93">
@@ -77433,7 +77435,7 @@
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="12" t="s">
+      <c r="A94" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B94">
@@ -77441,7 +77443,7 @@
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="12" t="s">
+      <c r="A95" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B95">
@@ -77449,7 +77451,7 @@
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="12" t="s">
+      <c r="A96" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B96">
@@ -77465,7 +77467,7 @@
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="12" t="s">
+      <c r="A98" s="11" t="s">
         <v>226</v>
       </c>
       <c r="B98">
@@ -77473,7 +77475,7 @@
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="12" t="s">
+      <c r="A99" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B99">
@@ -77481,7 +77483,7 @@
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="12" t="s">
+      <c r="A100" s="11" t="s">
         <v>153</v>
       </c>
       <c r="B100">
@@ -77489,7 +77491,7 @@
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="12" t="s">
+      <c r="A101" s="11" t="s">
         <v>149</v>
       </c>
       <c r="B101">
@@ -77497,7 +77499,7 @@
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="12" t="s">
+      <c r="A102" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B102">
@@ -77505,7 +77507,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="12" t="s">
+      <c r="A103" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B103">
@@ -77521,7 +77523,7 @@
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="12" t="s">
+      <c r="A105" s="11" t="s">
         <v>323</v>
       </c>
       <c r="B105">
@@ -77529,7 +77531,7 @@
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B106">
@@ -77537,7 +77539,7 @@
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="12" t="s">
+      <c r="A107" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B107">
@@ -77545,7 +77547,7 @@
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="12" t="s">
+      <c r="A108" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B108">
@@ -77553,7 +77555,7 @@
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="12" t="s">
+      <c r="A109" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B109">
@@ -77561,7 +77563,7 @@
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="12" t="s">
+      <c r="A110" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B110">
@@ -77577,7 +77579,7 @@
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="12" t="s">
+      <c r="A112" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B112">
@@ -77585,7 +77587,7 @@
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="12" t="s">
+      <c r="A113" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B113">
@@ -77593,7 +77595,7 @@
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="12" t="s">
+      <c r="A114" s="11" t="s">
         <v>318</v>
       </c>
       <c r="B114">
@@ -77601,7 +77603,7 @@
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="12" t="s">
+      <c r="A115" s="11" t="s">
         <v>313</v>
       </c>
       <c r="B115">
@@ -77609,7 +77611,7 @@
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="12" t="s">
+      <c r="A116" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B116">
@@ -77617,7 +77619,7 @@
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="12" t="s">
+      <c r="A117" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B117">
@@ -77625,7 +77627,7 @@
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="12" t="s">
+      <c r="A118" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B118">
@@ -77641,7 +77643,7 @@
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="12" t="s">
+      <c r="A120" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B120">
@@ -77649,7 +77651,7 @@
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="12" t="s">
+      <c r="A121" s="11" t="s">
         <v>226</v>
       </c>
       <c r="B121">
@@ -77657,7 +77659,7 @@
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="12" t="s">
+      <c r="A122" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B122">
@@ -77673,7 +77675,7 @@
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="12" t="s">
+      <c r="A124" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B124">
@@ -77681,7 +77683,7 @@
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="12" t="s">
+      <c r="A125" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B125">
@@ -77689,7 +77691,7 @@
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="12" t="s">
+      <c r="A126" s="11" t="s">
         <v>226</v>
       </c>
       <c r="B126">
@@ -77697,7 +77699,7 @@
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="12" t="s">
+      <c r="A127" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B127">
@@ -77705,7 +77707,7 @@
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="12" t="s">
+      <c r="A128" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B128">
@@ -77713,7 +77715,7 @@
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="12" t="s">
+      <c r="A129" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B129">
@@ -77721,7 +77723,7 @@
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="12" t="s">
+      <c r="A130" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B130">
@@ -77737,7 +77739,7 @@
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="12" t="s">
+      <c r="A132" s="11" t="s">
         <v>233</v>
       </c>
       <c r="B132">
@@ -77745,7 +77747,7 @@
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="12" t="s">
+      <c r="A133" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B133">
@@ -77753,7 +77755,7 @@
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="12" t="s">
+      <c r="A134" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B134">
@@ -77761,7 +77763,7 @@
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="12" t="s">
+      <c r="A135" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B135">
